--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_los lagos.xlsx
@@ -111,12 +111,12 @@
     <t xml:space="preserve">Quellón</t>
   </si>
   <si>
+    <t xml:space="preserve">Hualaihué</t>
+  </si>
+  <si>
     <t xml:space="preserve">Curaco de Vélez</t>
   </si>
   <si>
-    <t xml:space="preserve">Hualaihué</t>
-  </si>
-  <si>
     <t xml:space="preserve">Puqueldón</t>
   </si>
   <si>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:31</t>
+    <t xml:space="preserve">2026-09-09 23:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -990,7 +990,7 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>10204</v>
+        <v>10403</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2018</v>
@@ -1007,7 +1007,7 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>10403</v>
+        <v>10204</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2018</v>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:28</t>
+    <t xml:space="preserve">2026-09-17 14:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_los lagos.xlsx
@@ -111,12 +111,12 @@
     <t xml:space="preserve">Quellón</t>
   </si>
   <si>
+    <t xml:space="preserve">Curaco de Vélez</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hualaihué</t>
   </si>
   <si>
-    <t xml:space="preserve">Curaco de Vélez</t>
-  </si>
-  <si>
     <t xml:space="preserve">Puqueldón</t>
   </si>
   <si>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:23</t>
+    <t xml:space="preserve">2026-09-23 12:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -990,7 +990,7 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>10403</v>
+        <v>10204</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2018</v>
@@ -1007,7 +1007,7 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>10204</v>
+        <v>10403</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2018</v>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_los lagos.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:51</t>
+    <t xml:space="preserve">2026-10-01 23:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre salario mínimo (%)</t>
+    <t xml:space="preserve">% con ingreso igual al mínimo</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -166,9 +166,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre salario mínimo</t>
   </si>
 </sst>
 </file>
@@ -1144,7 +1141,7 @@
         <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:15</t>
+    <t xml:space="preserve">2026-10-02 11:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:23</t>
+    <t xml:space="preserve">2026-10-02 13:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2018_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:56</t>
+    <t xml:space="preserve">2026-10-05 12:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
